--- a/output/roomself_excel/11685.xlsx
+++ b/output/roomself_excel/11685.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94320</v>
+        <v>59862</v>
       </c>
       <c r="D2" t="n">
-        <v>2488</v>
+        <v>2012</v>
       </c>
       <c r="E2" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>318397</v>
+        <v>122211</v>
       </c>
       <c r="D3" t="n">
-        <v>6856</v>
+        <v>2804</v>
       </c>
       <c r="E3" t="n">
-        <v>905</v>
+        <v>338</v>
       </c>
       <c r="F3" t="n">
-        <v>634</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13387</v>
+        <v>54039</v>
       </c>
       <c r="D4" t="n">
-        <v>992</v>
+        <v>1880</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>232</v>
       </c>
       <c r="F4" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24472</v>
+        <v>94320</v>
       </c>
       <c r="D5" t="n">
-        <v>1252</v>
+        <v>2488</v>
       </c>
       <c r="E5" t="n">
-        <v>152</v>
+        <v>383</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42019</v>
+        <v>82285</v>
       </c>
       <c r="D6" t="n">
-        <v>1704</v>
+        <v>2568</v>
       </c>
       <c r="E6" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -590,6 +590,72 @@
       </c>
       <c r="F7" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13387</v>
+      </c>
+      <c r="D8" t="n">
+        <v>992</v>
+      </c>
+      <c r="E8" t="n">
+        <v>87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24472</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E9" t="n">
+        <v>152</v>
+      </c>
+      <c r="F9" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>42019</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1704</v>
+      </c>
+      <c r="E10" t="n">
+        <v>250</v>
+      </c>
+      <c r="F10" t="n">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11685.xlsx
+++ b/output/roomself_excel/11685.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2012</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>2804</v>
       </c>
-      <c r="E3" t="n">
-        <v>338</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>327</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>361</v>
+      </c>
+      <c r="J3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>1880</v>
       </c>
-      <c r="E4" t="n">
-        <v>232</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>227</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>221</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2488</v>
       </c>
-      <c r="E5" t="n">
-        <v>383</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>285</v>
+        <v>262</v>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>360</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>2568</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +661,20 @@
       <c r="D7" t="n">
         <v>836</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>169</v>
       </c>
-      <c r="F7" t="n">
-        <v>23</v>
-      </c>
+      <c r="G7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>992</v>
       </c>
-      <c r="E8" t="n">
-        <v>87</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>85</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>1252</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>152</v>
       </c>
-      <c r="F9" t="n">
-        <v>23</v>
-      </c>
+      <c r="G9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +751,27 @@
       <c r="D10" t="n">
         <v>1704</v>
       </c>
-      <c r="E10" t="n">
-        <v>250</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>222</v>
+        <v>227</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>199</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
